--- a/july 2026/GT_JULY_26/22-07-2026/Updated.xlsx
+++ b/july 2026/GT_JULY_26/22-07-2026/Updated.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr filterPrivacy="1" codeName="ThisWorkbook" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9556FB86-0F8D-4D09-B6F0-3D0DA66C6A2C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC8CE233-A314-4C59-9C0F-184F15EB5CE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="949" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3221,7 +3221,7 @@
       <c r="M4" s="238"/>
       <c r="N4" s="252">
         <f ca="1">TODAY()</f>
-        <v>46220</v>
+        <v>46225</v>
       </c>
       <c r="O4" s="252"/>
       <c r="P4" s="252"/>
@@ -3249,7 +3249,7 @@
       <c r="M5" s="238"/>
       <c r="N5" s="252">
         <f ca="1">N4-1</f>
-        <v>46219</v>
+        <v>46224</v>
       </c>
       <c r="O5" s="239"/>
       <c r="P5" s="239"/>
@@ -4438,7 +4438,7 @@
       <c r="M4" s="238"/>
       <c r="N4" s="252">
         <f ca="1">TODAY()</f>
-        <v>46220</v>
+        <v>46225</v>
       </c>
       <c r="O4" s="252"/>
       <c r="P4" s="252"/>
@@ -4466,7 +4466,7 @@
       <c r="M5" s="238"/>
       <c r="N5" s="252">
         <f ca="1">N4-1</f>
-        <v>46219</v>
+        <v>46224</v>
       </c>
       <c r="O5" s="239"/>
       <c r="P5" s="239"/>
@@ -5655,7 +5655,7 @@
       <c r="M4" s="238"/>
       <c r="N4" s="252">
         <f ca="1">TODAY()</f>
-        <v>46220</v>
+        <v>46225</v>
       </c>
       <c r="O4" s="252"/>
       <c r="P4" s="252"/>
@@ -5683,7 +5683,7 @@
       <c r="M5" s="238"/>
       <c r="N5" s="252">
         <f ca="1">N4-1</f>
-        <v>46219</v>
+        <v>46224</v>
       </c>
       <c r="O5" s="239"/>
       <c r="P5" s="239"/>
@@ -6872,7 +6872,7 @@
       <c r="M4" s="238"/>
       <c r="N4" s="252">
         <f ca="1">TODAY()</f>
-        <v>46220</v>
+        <v>46225</v>
       </c>
       <c r="O4" s="252"/>
       <c r="P4" s="252"/>
@@ -6900,7 +6900,7 @@
       <c r="M5" s="238"/>
       <c r="N5" s="252">
         <f ca="1">N4-1</f>
-        <v>46219</v>
+        <v>46224</v>
       </c>
       <c r="O5" s="239"/>
       <c r="P5" s="239"/>
@@ -8089,7 +8089,7 @@
       <c r="M4" s="238"/>
       <c r="N4" s="252">
         <f ca="1">TODAY()</f>
-        <v>46220</v>
+        <v>46225</v>
       </c>
       <c r="O4" s="252"/>
       <c r="P4" s="252"/>
@@ -8117,7 +8117,7 @@
       <c r="M5" s="238"/>
       <c r="N5" s="252">
         <f ca="1">N4-1</f>
-        <v>46219</v>
+        <v>46224</v>
       </c>
       <c r="O5" s="239"/>
       <c r="P5" s="239"/>
@@ -9306,7 +9306,7 @@
       <c r="M4" s="238"/>
       <c r="N4" s="252">
         <f ca="1">TODAY()</f>
-        <v>46220</v>
+        <v>46225</v>
       </c>
       <c r="O4" s="252"/>
       <c r="P4" s="252"/>
@@ -9334,7 +9334,7 @@
       <c r="M5" s="238"/>
       <c r="N5" s="252">
         <f ca="1">N4-1</f>
-        <v>46219</v>
+        <v>46224</v>
       </c>
       <c r="O5" s="239"/>
       <c r="P5" s="239"/>
@@ -10523,7 +10523,7 @@
       <c r="M4" s="238"/>
       <c r="N4" s="252">
         <f ca="1">TODAY()</f>
-        <v>46220</v>
+        <v>46225</v>
       </c>
       <c r="O4" s="252"/>
       <c r="P4" s="252"/>
@@ -10551,7 +10551,7 @@
       <c r="M5" s="238"/>
       <c r="N5" s="252">
         <f ca="1">N4-1</f>
-        <v>46219</v>
+        <v>46224</v>
       </c>
       <c r="O5" s="239"/>
       <c r="P5" s="239"/>
@@ -11740,7 +11740,7 @@
       <c r="M4" s="238"/>
       <c r="N4" s="252">
         <f ca="1">TODAY()</f>
-        <v>46220</v>
+        <v>46225</v>
       </c>
       <c r="O4" s="252"/>
       <c r="P4" s="252"/>
@@ -11768,7 +11768,7 @@
       <c r="M5" s="238"/>
       <c r="N5" s="252">
         <f ca="1">N4-1</f>
-        <v>46219</v>
+        <v>46224</v>
       </c>
       <c r="O5" s="239"/>
       <c r="P5" s="239"/>
@@ -12957,7 +12957,7 @@
       <c r="M4" s="238"/>
       <c r="N4" s="252">
         <f ca="1">TODAY()</f>
-        <v>46220</v>
+        <v>46225</v>
       </c>
       <c r="O4" s="252"/>
       <c r="P4" s="252"/>
@@ -12985,7 +12985,7 @@
       <c r="M5" s="238"/>
       <c r="N5" s="252">
         <f ca="1">N4-1</f>
-        <v>46219</v>
+        <v>46224</v>
       </c>
       <c r="O5" s="239"/>
       <c r="P5" s="239"/>
@@ -14174,7 +14174,7 @@
       <c r="M4" s="238"/>
       <c r="N4" s="252">
         <f ca="1">TODAY()</f>
-        <v>46220</v>
+        <v>46225</v>
       </c>
       <c r="O4" s="252"/>
       <c r="P4" s="252"/>
@@ -14202,7 +14202,7 @@
       <c r="M5" s="238"/>
       <c r="N5" s="252">
         <f ca="1">N4-1</f>
-        <v>46219</v>
+        <v>46224</v>
       </c>
       <c r="O5" s="239"/>
       <c r="P5" s="239"/>
@@ -18141,7 +18141,7 @@
       <c r="M4" s="238"/>
       <c r="N4" s="252">
         <f ca="1">TODAY()</f>
-        <v>46220</v>
+        <v>46225</v>
       </c>
       <c r="O4" s="252"/>
       <c r="P4" s="252"/>
@@ -18169,7 +18169,7 @@
       <c r="M5" s="238"/>
       <c r="N5" s="252">
         <f ca="1">N4-1</f>
-        <v>46219</v>
+        <v>46224</v>
       </c>
       <c r="O5" s="239"/>
       <c r="P5" s="239"/>
@@ -19358,7 +19358,7 @@
       <c r="M4" s="238"/>
       <c r="N4" s="252">
         <f ca="1">TODAY()</f>
-        <v>46220</v>
+        <v>46225</v>
       </c>
       <c r="O4" s="252"/>
       <c r="P4" s="252"/>
@@ -19386,7 +19386,7 @@
       <c r="M5" s="238"/>
       <c r="N5" s="252">
         <f ca="1">N4-1</f>
-        <v>46219</v>
+        <v>46224</v>
       </c>
       <c r="O5" s="239"/>
       <c r="P5" s="239"/>
@@ -20575,7 +20575,7 @@
       <c r="M4" s="238"/>
       <c r="N4" s="252">
         <f ca="1">TODAY()</f>
-        <v>46220</v>
+        <v>46225</v>
       </c>
       <c r="O4" s="252"/>
       <c r="P4" s="252"/>
@@ -20603,7 +20603,7 @@
       <c r="M5" s="238"/>
       <c r="N5" s="252">
         <f ca="1">N4-1</f>
-        <v>46219</v>
+        <v>46224</v>
       </c>
       <c r="O5" s="239"/>
       <c r="P5" s="239"/>
@@ -21792,7 +21792,7 @@
       <c r="M4" s="238"/>
       <c r="N4" s="252">
         <f ca="1">TODAY()</f>
-        <v>46220</v>
+        <v>46225</v>
       </c>
       <c r="O4" s="252"/>
       <c r="P4" s="252"/>
@@ -21820,7 +21820,7 @@
       <c r="M5" s="238"/>
       <c r="N5" s="252">
         <f ca="1">N4-1</f>
-        <v>46219</v>
+        <v>46224</v>
       </c>
       <c r="O5" s="239"/>
       <c r="P5" s="239"/>
@@ -23011,7 +23011,7 @@
       <c r="M4" s="238"/>
       <c r="N4" s="252">
         <f ca="1">TODAY()</f>
-        <v>46220</v>
+        <v>46225</v>
       </c>
       <c r="O4" s="252"/>
       <c r="P4" s="252"/>
@@ -23039,7 +23039,7 @@
       <c r="M5" s="238"/>
       <c r="N5" s="252">
         <f ca="1">N4-1</f>
-        <v>46219</v>
+        <v>46224</v>
       </c>
       <c r="O5" s="239"/>
       <c r="P5" s="239"/>
@@ -24596,7 +24596,7 @@
       <c r="M4" s="238"/>
       <c r="N4" s="252">
         <f ca="1">TODAY()</f>
-        <v>46220</v>
+        <v>46225</v>
       </c>
       <c r="O4" s="252"/>
       <c r="P4" s="252"/>
@@ -24624,7 +24624,7 @@
       <c r="M5" s="238"/>
       <c r="N5" s="252">
         <f ca="1">N4-1</f>
-        <v>46219</v>
+        <v>46224</v>
       </c>
       <c r="O5" s="239"/>
       <c r="P5" s="239"/>
@@ -26092,7 +26092,7 @@
       <c r="M4" s="238"/>
       <c r="N4" s="252">
         <f ca="1">TODAY()</f>
-        <v>46220</v>
+        <v>46225</v>
       </c>
       <c r="O4" s="252"/>
       <c r="P4" s="252"/>
@@ -26120,7 +26120,7 @@
       <c r="M5" s="238"/>
       <c r="N5" s="252">
         <f ca="1">N4-1</f>
-        <v>46219</v>
+        <v>46224</v>
       </c>
       <c r="O5" s="239"/>
       <c r="P5" s="239"/>
@@ -27309,7 +27309,7 @@
       <c r="M4" s="238"/>
       <c r="N4" s="252">
         <f ca="1">TODAY()</f>
-        <v>46220</v>
+        <v>46225</v>
       </c>
       <c r="O4" s="252"/>
       <c r="P4" s="252"/>
@@ -27337,7 +27337,7 @@
       <c r="M5" s="238"/>
       <c r="N5" s="252">
         <f ca="1">N4-1</f>
-        <v>46219</v>
+        <v>46224</v>
       </c>
       <c r="O5" s="239"/>
       <c r="P5" s="239"/>
@@ -28525,7 +28525,7 @@
       <c r="M4" s="238"/>
       <c r="N4" s="252">
         <f ca="1">TODAY()</f>
-        <v>46220</v>
+        <v>46225</v>
       </c>
       <c r="O4" s="252"/>
       <c r="P4" s="252"/>
@@ -28553,7 +28553,7 @@
       <c r="M5" s="238"/>
       <c r="N5" s="252">
         <f ca="1">N4-1</f>
-        <v>46219</v>
+        <v>46224</v>
       </c>
       <c r="O5" s="239"/>
       <c r="P5" s="239"/>
@@ -29742,7 +29742,7 @@
       <c r="M4" s="238"/>
       <c r="N4" s="252">
         <f ca="1">TODAY()</f>
-        <v>46220</v>
+        <v>46225</v>
       </c>
       <c r="O4" s="252"/>
       <c r="P4" s="252"/>
@@ -29770,7 +29770,7 @@
       <c r="M5" s="238"/>
       <c r="N5" s="252">
         <f ca="1">N4-1</f>
-        <v>46219</v>
+        <v>46224</v>
       </c>
       <c r="O5" s="239"/>
       <c r="P5" s="239"/>
@@ -30959,7 +30959,7 @@
       <c r="M4" s="238"/>
       <c r="N4" s="252">
         <f ca="1">TODAY()</f>
-        <v>46220</v>
+        <v>46225</v>
       </c>
       <c r="O4" s="252"/>
       <c r="P4" s="252"/>
@@ -30987,7 +30987,7 @@
       <c r="M5" s="238"/>
       <c r="N5" s="252">
         <f ca="1">N4-1</f>
-        <v>46219</v>
+        <v>46224</v>
       </c>
       <c r="O5" s="239"/>
       <c r="P5" s="239"/>
